--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -85,55 +85,112 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>UZIEL</t>
+  </si>
+  <si>
+    <t>LIA SARED</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
     <t>JOSE ABEL</t>
   </si>
   <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>SANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
   </si>
   <si>
     <t>BRENDA</t>
-  </si>
-  <si>
-    <t>MELANI YOSELIN</t>
   </si>
   <si>
     <t>LEONEL</t>
@@ -732,16 +789,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,16 +815,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>38.24</v>
+      </c>
+      <c r="H3">
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -801,16 +864,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>47.83</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -824,16 +890,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -847,16 +916,19 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>68.18000000000001</v>
+      </c>
+      <c r="H7">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -912,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>77.5</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -938,16 +1010,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>88.23999999999999</v>
+        <v>38.24</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -999,7 +1071,7 @@
         <v>47.83</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1016,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1042,13 +1114,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>72.73</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H7">
         <v>6.3</v>
@@ -1061,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1093,16 +1165,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920144</v>
+        <v>24330051920122</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1116,22 +1188,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920122</v>
+        <v>24330051920170</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1139,22 +1211,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920255</v>
+        <v>24330051920206</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1162,39 +1234,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920229</v>
+        <v>24330051920277</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920368</v>
+        <v>24330051920256</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1203,29 +1275,190 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920391</v>
+        <v>24330051920257</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920144</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920180</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920184</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920190</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920229</v>
+      </c>
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920391</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
         <v>14</v>
       </c>
-      <c r="G7">
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -91,12 +91,18 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
     <t>PORTUGAL</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -109,15 +115,9 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
@@ -127,12 +127,18 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
     <t>TLAXCALTECA</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>CAMACHO</t>
   </si>
   <si>
@@ -142,15 +148,9 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -163,12 +163,18 @@
     <t>LIA SARED</t>
   </si>
   <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>GAEL ARMANDO</t>
   </si>
   <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
     <t>IRVING JESUS</t>
   </si>
   <si>
@@ -181,13 +187,7 @@
     <t>JOSE ABEL</t>
   </si>
   <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
     <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
   </si>
   <si>
     <t>BRENDA</t>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920206</v>
+        <v>24330051920180</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920277</v>
+        <v>24330051920206</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920256</v>
+        <v>24330051920277</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1272,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920257</v>
+        <v>24330051920190</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1295,7 +1295,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1303,13 +1303,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920131</v>
+        <v>24330051920256</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
         <v>52</v>
@@ -1318,21 +1318,21 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920144</v>
+        <v>24330051920257</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>53</v>
@@ -1341,21 +1341,21 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920180</v>
+        <v>24330051920131</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>54</v>
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920184</v>
+        <v>24330051920144</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1387,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920190</v>
+        <v>24330051920184</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -85,15 +85,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>HILARIO</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>PORTUGAL</t>
   </si>
   <si>
@@ -103,6 +103,9 @@
     <t>ROSAS</t>
   </si>
   <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -115,21 +118,24 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>CAMACHO</t>
   </si>
   <si>
@@ -148,24 +157,24 @@
     <t>CORONA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
     <t>LIA SARED</t>
   </si>
   <si>
     <t>MARLENE</t>
   </si>
   <si>
+    <t>SANDRA PAOLA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
@@ -175,6 +184,9 @@
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>ARELI CICLARI</t>
+  </si>
+  <si>
     <t>IRVING JESUS</t>
   </si>
   <si>
@@ -187,10 +199,13 @@
     <t>JOSE ABEL</t>
   </si>
   <si>
-    <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
+    <t>MARELY</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALIN MARIEL</t>
   </si>
   <si>
     <t>LEONEL</t>
@@ -841,16 +856,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1036,16 +1054,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>81.81999999999999</v>
+        <v>63.64</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1133,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1165,22 +1183,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920122</v>
+        <v>24330051920170</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1188,16 +1206,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920170</v>
+        <v>24330051920180</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1211,16 +1229,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920180</v>
+        <v>24330051920184</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1240,10 +1258,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1263,10 +1281,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1286,10 +1304,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1303,22 +1321,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920256</v>
+        <v>24330051920217</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1326,16 +1344,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920257</v>
+        <v>24330051920256</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1349,39 +1367,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920131</v>
+        <v>24330051920257</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920144</v>
+        <v>24330051920131</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1395,22 +1413,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920184</v>
+        <v>24330051920144</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1418,16 +1436,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920229</v>
+        <v>24330051920228</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1441,24 +1459,70 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920391</v>
+        <v>24330051920230</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920246</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920391</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
         <v>14</v>
       </c>
-      <c r="G14">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -85,39 +85,45 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>HILARIO</t>
   </si>
   <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
@@ -130,33 +136,39 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -166,37 +178,43 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>UZIEL</t>
+  </si>
+  <si>
     <t>LIA SARED</t>
   </si>
   <si>
     <t>MARLENE</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>JOSE ABEL</t>
+  </si>
+  <si>
     <t>SANDRA PAOLA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
     <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
-    <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
   </si>
   <si>
     <t>MARELY</t>
@@ -1151,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1183,22 +1201,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920170</v>
+        <v>24330051920122</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1206,16 +1224,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920180</v>
+        <v>24330051920170</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1229,16 +1247,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920184</v>
+        <v>24330051920180</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1258,10 +1276,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1281,10 +1299,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1304,10 +1322,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1321,22 +1339,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920217</v>
+        <v>24330051920256</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1344,16 +1362,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920256</v>
+        <v>24330051920257</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1367,22 +1385,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920257</v>
+        <v>23330051920211</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1396,10 +1414,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1419,10 +1437,10 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1436,22 +1454,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920228</v>
+        <v>24330051920184</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1459,16 +1477,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920230</v>
+        <v>24330051920217</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1482,16 +1500,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920246</v>
+        <v>24330051920228</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1505,24 +1523,70 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920391</v>
+        <v>24330051920230</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920246</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920391</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
         <v>14</v>
       </c>
-      <c r="G16">
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="133">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,81 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DURAN</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>RIOS</t>
   </si>
   <si>
@@ -100,18 +175,9 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>CHONCOA</t>
   </si>
   <si>
@@ -127,21 +193,78 @@
     <t>MORA</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>ZUNO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
     <t>VEGA</t>
   </si>
   <si>
@@ -154,9 +277,6 @@
     <t>CAMACHO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -169,13 +289,85 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
   </si>
   <si>
     <t>UZIEL</t>
@@ -185,9 +377,6 @@
   </si>
   <si>
     <t>MARLENE</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>GAEL ARMANDO</t>
@@ -1169,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1201,16 +1390,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920122</v>
+        <v>24330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1219,67 +1408,67 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920170</v>
+        <v>24330051920410</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920180</v>
+        <v>24330051920143</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920206</v>
+        <v>24330051920400</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1288,21 +1477,21 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920277</v>
+        <v>24330051920213</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1311,21 +1500,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920190</v>
+        <v>24330051920187</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1334,259 +1523,880 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920256</v>
+        <v>24330051920201</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920257</v>
+        <v>24330051920194</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920211</v>
+        <v>24330051920247</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920131</v>
+        <v>24330051920274</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920144</v>
+        <v>24330051920267</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920184</v>
+        <v>24330051920369</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920217</v>
+        <v>24330051920283</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920228</v>
+        <v>23330051920189</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920230</v>
+        <v>23330051920195</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920246</v>
+        <v>23330051920202</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920391</v>
+        <v>24330051920155</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920147</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920315</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920355</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920388</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920188</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920316</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920330</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920255</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920390</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920122</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>24330051920170</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920180</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>24330051920206</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920277</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>24330051920190</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>24330051920256</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>24330051920257</v>
+      </c>
+      <c r="B36" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="C36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>23330051920211</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>24330051920131</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>24330051920144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>24330051920184</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>24330051920217</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>24330051920228</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>24330051920230</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>24330051920246</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>24330051920391</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" t="s">
+        <v>132</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
         <v>14</v>
       </c>
-      <c r="G18">
+      <c r="G45">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="159">
   <si>
     <t>Mat</t>
   </si>
@@ -85,334 +85,412 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
     <t>DURAN</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
     <t>PANZO</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>RAMON</t>
   </si>
   <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>RUL</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZOPILLAXTLE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PINO</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ERWIN ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS DAMIAN</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
   </si>
   <si>
     <t>EDWARD ALEXIS</t>
   </si>
   <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>IRVING EMILIO</t>
+  </si>
+  <si>
+    <t>MAYRIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>LEVI SANTIAGO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>MIRANDA ALIZEET</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>JOSE GABRIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>JOSE ABEL</t>
+  </si>
+  <si>
     <t>EDILBERTO</t>
   </si>
   <si>
-    <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>SANDY CAMILA</t>
-  </si>
-  <si>
-    <t>AYLIN ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUZ ARIANA</t>
-  </si>
-  <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>YARETZY NAOMI</t>
+    <t>UZIEL</t>
+  </si>
+  <si>
+    <t>LIA SARED</t>
+  </si>
+  <si>
+    <t>SANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ARELI CICLARI</t>
+  </si>
+  <si>
+    <t>MARELY</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALIN MARIEL</t>
   </si>
   <si>
     <t>BRYAN</t>
   </si>
   <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>DEREK</t>
-  </si>
-  <si>
-    <t>CARLOS ARGEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
     <t>ERNESTO</t>
   </si>
   <si>
-    <t>MARBELY YOSELIN</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
     <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>MARELY</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALIN MARIEL</t>
   </si>
   <si>
     <t>LEONEL</t>
@@ -1358,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1390,16 +1468,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920156</v>
+        <v>24330051920101</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1413,16 +1491,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920410</v>
+        <v>24330051920104</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1436,16 +1514,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920143</v>
+        <v>24330051920393</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1459,22 +1537,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920400</v>
+        <v>24330051920260</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1482,22 +1560,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920213</v>
+        <v>23330051920189</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1505,22 +1583,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920187</v>
+        <v>23330051920195</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1528,22 +1606,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920201</v>
+        <v>23330051920202</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1551,229 +1629,229 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920194</v>
+        <v>24330051920156</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920247</v>
+        <v>24330051920400</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920274</v>
+        <v>24330051920355</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920267</v>
+        <v>24330051920213</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920369</v>
+        <v>24330051920394</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920283</v>
+        <v>24330051920406</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920189</v>
+        <v>24330051920389</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920195</v>
+        <v>24330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920202</v>
+        <v>24330051920407</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920155</v>
+        <v>24330051920409</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -1781,22 +1859,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920147</v>
+        <v>24330051920258</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1804,22 +1882,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920113</v>
+        <v>24330051920405</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -1827,22 +1905,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920315</v>
+        <v>24330051920369</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>3</v>
@@ -1850,183 +1928,183 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920355</v>
+        <v>24330051920392</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
         <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920388</v>
+        <v>24330051920155</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920188</v>
+        <v>24330051920147</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920316</v>
+        <v>24330051920107</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920330</v>
+        <v>24330051920113</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920255</v>
+        <v>24330051920143</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920390</v>
+        <v>24330051920315</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920122</v>
+        <v>24330051920180</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -2034,16 +2112,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920170</v>
+        <v>24330051920388</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2057,16 +2135,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920180</v>
+        <v>24330051920187</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2080,16 +2158,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920206</v>
+        <v>24330051920188</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2103,16 +2181,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920277</v>
+        <v>24330051920190</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2126,16 +2204,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920190</v>
+        <v>24330051920201</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2149,22 +2227,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920256</v>
+        <v>24330051920194</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -2172,22 +2250,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920257</v>
+        <v>24330051920247</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2195,22 +2273,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920211</v>
+        <v>24330051920267</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2218,137 +2296,137 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920131</v>
+        <v>24330051920256</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>24330051920144</v>
+        <v>24330051920390</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>24330051920184</v>
+        <v>24330051920283</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>24330051920217</v>
+        <v>24330051920293</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>24330051920228</v>
+        <v>23330051920211</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>24330051920230</v>
+        <v>24330051920131</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2356,22 +2434,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>24330051920246</v>
+        <v>24330051920144</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2379,24 +2457,346 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
+        <v>24330051920410</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>24330051920122</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>24330051920170</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>24330051920184</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>24330051920316</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>24330051920206</v>
+      </c>
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>24330051920277</v>
+      </c>
+      <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" t="s">
+        <v>150</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>24330051920217</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>24330051920228</v>
+      </c>
+      <c r="B53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" t="s">
+        <v>152</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>24330051920230</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>153</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>24330051920246</v>
+      </c>
+      <c r="B55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" t="s">
+        <v>154</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>24330051920274</v>
+      </c>
+      <c r="B56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>24330051920255</v>
+      </c>
+      <c r="B57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" t="s">
+        <v>156</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>24330051920257</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" t="s">
+        <v>157</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
         <v>24330051920391</v>
       </c>
-      <c r="B45" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
         <v>14</v>
       </c>
-      <c r="G45">
+      <c r="G59">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="161">
   <si>
     <t>Mat</t>
   </si>
@@ -85,123 +85,123 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>DURAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>DURAN</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>HILARIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
@@ -217,61 +217,103 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>NIETO</t>
   </si>
   <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
+  </si>
+  <si>
+    <t>RUL</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>VIEYRA</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANIAGUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
   </si>
   <si>
     <t>ORTEGA</t>
@@ -280,220 +322,184 @@
     <t>ZOPILLAXTLE</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>RUL</t>
+    <t>CABRERA</t>
   </si>
   <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>MARIA ESTEFANIA</t>
   </si>
   <si>
     <t>ERWIN ISRAEL</t>
   </si>
   <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>DANIELA LILI</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>JESUS DAMIAN</t>
   </si>
   <si>
+    <t>EDWARD ALEXIS</t>
+  </si>
+  <si>
+    <t>CARLOS ARGEL</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>MAYRIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>IRVING JESUS</t>
+  </si>
+  <si>
+    <t>RUBEN</t>
+  </si>
+  <si>
+    <t>MARBELY YOSELIN</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JOSE GABRIEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>MIRANDA ALIZEET</t>
+  </si>
+  <si>
+    <t>DEREK</t>
+  </si>
+  <si>
+    <t>CARLOS ANTONIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>YURANI</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
     <t>NATANAHEL</t>
   </si>
   <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>EDWARD ALEXIS</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
+    <t>LEVI SANTIAGO</t>
+  </si>
+  <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>JOSE ABEL</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>UZIEL</t>
+  </si>
+  <si>
+    <t>LIA SARED</t>
   </si>
   <si>
     <t>MARIEL</t>
   </si>
   <si>
-    <t>SANDY CAMILA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>SANDRA PAOLA</t>
   </si>
   <si>
     <t>IRVING EMILIO</t>
   </si>
   <si>
-    <t>MAYRIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA LILI</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>LEVI SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>MIRANDA ALIZEET</t>
-  </si>
-  <si>
-    <t>DEREK</t>
-  </si>
-  <si>
-    <t>CARLOS ANTONIO</t>
-  </si>
-  <si>
-    <t>CARLOS ARGEL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
     <t>AYLIN ABIGAIL</t>
   </si>
   <si>
     <t>BENJAMIN</t>
   </si>
   <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
     <t>OCTAVIO</t>
   </si>
   <si>
     <t>LUZ ARIANA</t>
   </si>
   <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
-    <t>YARETZY NAOMI</t>
-  </si>
-  <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>IRVING JESUS</t>
-  </si>
-  <si>
-    <t>MARBELY YOSELIN</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>JOSE GABRIEL</t>
+    <t>ARELI CICLARI</t>
+  </si>
+  <si>
+    <t>MARELY</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALIN MARIEL</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
-  </si>
-  <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>MARELY</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALIN MARIEL</t>
-  </si>
-  <si>
-    <t>BRYAN</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1468,7 +1474,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920101</v>
+        <v>24330051920104</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1477,7 +1483,7 @@
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1491,16 +1497,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1514,22 +1520,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920393</v>
+        <v>24330051920394</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1537,7 +1543,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920260</v>
+        <v>24330051920330</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1546,13 +1552,13 @@
         <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1560,22 +1566,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920189</v>
+        <v>24330051920407</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1583,22 +1589,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920195</v>
+        <v>24330051920260</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1606,39 +1612,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920202</v>
+        <v>24330051920156</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920156</v>
+        <v>24330051920315</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1652,16 +1658,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920400</v>
+        <v>24330051920213</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1675,22 +1681,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920355</v>
+        <v>24330051920389</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1698,22 +1704,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920213</v>
+        <v>24330051920247</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -1721,22 +1727,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920394</v>
+        <v>24330051920409</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1744,22 +1750,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920406</v>
+        <v>24330051920256</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -1767,22 +1773,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920389</v>
+        <v>24330051920405</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -1790,22 +1796,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920330</v>
+        <v>24330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1813,16 +1819,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920407</v>
+        <v>24330051920369</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1836,22 +1842,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920409</v>
+        <v>24330051920293</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
         <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -1859,22 +1865,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920258</v>
+        <v>22330051920389</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
         <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1882,22 +1888,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920405</v>
+        <v>23330051920195</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
         <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -1905,22 +1911,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920369</v>
+        <v>23330051920332</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G21">
         <v>3</v>
@@ -1928,16 +1934,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920392</v>
+        <v>24330051920107</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1951,16 +1957,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920155</v>
+        <v>24330051920113</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1974,16 +1980,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920147</v>
+        <v>24330051920143</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1997,22 +2003,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920107</v>
+        <v>24330051920400</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2020,22 +2026,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920113</v>
+        <v>24330051920181</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -2043,22 +2049,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920143</v>
+        <v>24330051920388</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2066,22 +2072,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920315</v>
+        <v>24330051920194</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -2089,22 +2095,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920180</v>
+        <v>24330051920267</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -2112,22 +2118,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920388</v>
+        <v>24330051920258</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2135,22 +2141,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920187</v>
+        <v>24330051920283</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2158,22 +2164,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920188</v>
+        <v>23330051920189</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -2181,252 +2187,252 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920190</v>
+        <v>24330051920392</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
         <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920201</v>
+        <v>24330051920131</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920194</v>
+        <v>24330051920155</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920247</v>
+        <v>24330051920147</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920267</v>
+        <v>24330051920144</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920256</v>
+        <v>24330051920410</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>24330051920390</v>
+        <v>24330051920122</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>24330051920283</v>
+        <v>24330051920170</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>24330051920293</v>
+        <v>24330051920355</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920211</v>
+        <v>24330051920180</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>24330051920131</v>
+        <v>24330051920184</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2434,22 +2440,22 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>24330051920144</v>
+        <v>24330051920406</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2457,22 +2463,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>24330051920410</v>
+        <v>24330051920187</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2480,22 +2486,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>24330051920122</v>
+        <v>24330051920188</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2503,16 +2509,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>24330051920170</v>
+        <v>24330051920316</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2526,16 +2532,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>24330051920184</v>
+        <v>24330051920206</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2549,13 +2555,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>24330051920316</v>
+        <v>24330051920277</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
         <v>149</v>
@@ -2572,16 +2578,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>24330051920206</v>
+        <v>24330051920190</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D50" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2595,16 +2601,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>24330051920277</v>
+        <v>24330051920201</v>
       </c>
       <c r="B51" t="s">
         <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2624,10 +2630,10 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2647,10 +2653,10 @@
         <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2667,13 +2673,13 @@
         <v>24330051920230</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2693,10 +2699,10 @@
         <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2716,10 +2722,10 @@
         <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2736,13 +2742,13 @@
         <v>24330051920255</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2762,10 +2768,10 @@
         <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2782,13 +2788,13 @@
         <v>24330051920391</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2797,6 +2803,29 @@
         <v>14</v>
       </c>
       <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>23330051920211</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -151,69 +151,69 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>PORTUGAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -280,51 +280,51 @@
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PAYRO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>CHACON</t>
   </si>
   <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ZOPILLAXTLE</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -409,94 +409,94 @@
     <t>BETZY AYELEN</t>
   </si>
   <si>
+    <t>SERGIO ALAN</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LEVI SANTIAGO</t>
+  </si>
+  <si>
+    <t>EMMANUEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>JOSE ABEL</t>
+  </si>
+  <si>
+    <t>EDILBERTO</t>
+  </si>
+  <si>
+    <t>UZIEL</t>
+  </si>
+  <si>
+    <t>LIA SARED</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>SANDRA PAOLA</t>
+  </si>
+  <si>
+    <t>IRVING EMILIO</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>BENJAMIN</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>GAEL ARMANDO</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>ARELI CICLARI</t>
+  </si>
+  <si>
+    <t>MARELY</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALIN MARIEL</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
     <t>GABRIEL URYEL</t>
   </si>
   <si>
-    <t>SERGIO ALAN</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
   </si>
   <si>
     <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>LEVI SANTIAGO</t>
-  </si>
-  <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>JOSE ABEL</t>
-  </si>
-  <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
-  </si>
-  <si>
-    <t>IRVING EMILIO</t>
-  </si>
-  <si>
-    <t>AYLIN ABIGAIL</t>
-  </si>
-  <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>LUZ ARIANA</t>
-  </si>
-  <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>MARELY</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALIN MARIEL</t>
-  </si>
-  <si>
-    <t>BRYAN</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
@@ -1503,7 +1503,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>104</v>
@@ -1687,7 +1687,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
@@ -2095,13 +2095,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920267</v>
+        <v>24330051920258</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
         <v>130</v>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920258</v>
+        <v>24330051920283</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
         <v>131</v>
@@ -2133,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2141,13 +2141,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920283</v>
+        <v>24330051920392</v>
       </c>
       <c r="B31" t="s">
         <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
         <v>132</v>
@@ -2156,44 +2156,44 @@
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920189</v>
+        <v>24330051920131</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
         <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920392</v>
+        <v>24330051920155</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
         <v>134</v>
@@ -2210,13 +2210,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920131</v>
+        <v>24330051920147</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
         <v>135</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920155</v>
+        <v>24330051920144</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
         <v>89</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920147</v>
+        <v>24330051920410</v>
       </c>
       <c r="B36" t="s">
         <v>49</v>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920144</v>
+        <v>24330051920122</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
         <v>91</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920410</v>
+        <v>24330051920170</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="D38" t="s">
         <v>139</v>
@@ -2317,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2325,13 +2325,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>24330051920122</v>
+        <v>24330051920355</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D39" t="s">
         <v>140</v>
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>24330051920170</v>
+        <v>24330051920180</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
         <v>141</v>
@@ -2371,13 +2371,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>24330051920355</v>
+        <v>24330051920184</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
         <v>142</v>
@@ -2394,13 +2394,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>24330051920180</v>
+        <v>24330051920406</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
         <v>143</v>
@@ -2417,13 +2417,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>24330051920184</v>
+        <v>24330051920187</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
         <v>144</v>
@@ -2440,13 +2440,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>24330051920406</v>
+        <v>24330051920188</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
         <v>145</v>
@@ -2463,13 +2463,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>24330051920187</v>
+        <v>24330051920316</v>
       </c>
       <c r="B45" t="s">
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
         <v>146</v>
@@ -2486,16 +2486,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>24330051920188</v>
+        <v>24330051920206</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2509,16 +2509,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>24330051920316</v>
+        <v>24330051920277</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
         <v>96</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2532,16 +2532,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>24330051920206</v>
+        <v>24330051920190</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
         <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>24330051920277</v>
+        <v>24330051920201</v>
       </c>
       <c r="B49" t="s">
         <v>59</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>24330051920190</v>
+        <v>24330051920217</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
         <v>99</v>
@@ -2593,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2601,13 +2601,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>24330051920201</v>
+        <v>24330051920228</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
         <v>151</v>
@@ -2616,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2624,13 +2624,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>24330051920217</v>
+        <v>24330051920230</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
         <v>152</v>
@@ -2647,13 +2647,13 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>24330051920228</v>
+        <v>24330051920246</v>
       </c>
       <c r="B53" t="s">
         <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
         <v>153</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>24330051920230</v>
+        <v>24330051920274</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D54" t="s">
         <v>154</v>
@@ -2685,7 +2685,7 @@
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>24330051920246</v>
+        <v>24330051920267</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D55" t="s">
         <v>155</v>
@@ -2708,7 +2708,7 @@
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2716,13 +2716,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>24330051920274</v>
+        <v>24330051920255</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s">
         <v>156</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>24330051920255</v>
+        <v>24330051920257</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D57" t="s">
         <v>157</v>
@@ -2762,13 +2762,13 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>24330051920257</v>
+        <v>24330051920391</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D58" t="s">
         <v>158</v>
@@ -2777,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2785,22 +2785,22 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>24330051920391</v>
+        <v>23330051920189</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C59" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
         <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G59">
         <v>1</v>

--- a/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="114">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
@@ -112,6 +109,9 @@
     <t>GUERRA</t>
   </si>
   <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
@@ -127,208 +127,130 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>PANIAGUA</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
+    <t>RUL</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
-    <t>PORTUGAL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>NIETO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>PANIAGUA</t>
-  </si>
-  <si>
-    <t>RUL</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PAYRO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ZOPILLAXTLE</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>CHACON</t>
   </si>
   <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MARIA ESTEFANIA</t>
+    <t>PALACIOS</t>
   </si>
   <si>
     <t>ERWIN ISRAEL</t>
@@ -355,6 +277,9 @@
     <t>SANDY CAMILA</t>
   </si>
   <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
     <t>MAYRIN GUADALUPE</t>
   </si>
   <si>
@@ -379,30 +304,15 @@
     <t>JOSE GABRIEL</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>MIRANDA ALIZEET</t>
-  </si>
-  <si>
     <t>DEREK</t>
   </si>
   <si>
-    <t>CARLOS ANTONIO</t>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
-    <t>YURANI</t>
-  </si>
-  <si>
     <t>JANNIHA YUVIETH</t>
   </si>
   <si>
@@ -412,40 +322,19 @@
     <t>SERGIO ALAN</t>
   </si>
   <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
     <t>LEVI SANTIAGO</t>
   </si>
   <si>
-    <t>EMMANUEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
+    <t>BRYANA</t>
   </si>
   <si>
     <t>JOSE ABEL</t>
   </si>
   <si>
-    <t>EDILBERTO</t>
-  </si>
-  <si>
-    <t>UZIEL</t>
-  </si>
-  <si>
-    <t>LIA SARED</t>
-  </si>
-  <si>
     <t>MARIEL</t>
   </si>
   <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>SANDRA PAOLA</t>
+    <t>AMISADAY</t>
   </si>
   <si>
     <t>IRVING EMILIO</t>
@@ -454,33 +343,12 @@
     <t>AYLIN ABIGAIL</t>
   </si>
   <si>
-    <t>BENJAMIN</t>
-  </si>
-  <si>
     <t>JIMENA</t>
   </si>
   <si>
-    <t>GAEL ARMANDO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
     <t>LUZ ARIANA</t>
   </si>
   <si>
-    <t>ARELI CICLARI</t>
-  </si>
-  <si>
-    <t>MARELY</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALIN MARIEL</t>
-  </si>
-  <si>
     <t>BRYAN</t>
   </si>
   <si>
@@ -490,16 +358,7 @@
     <t>ERNESTO</t>
   </si>
   <si>
-    <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
+    <t>ANGEL OSWALDO</t>
   </si>
 </sst>
 </file>
@@ -1293,13 +1152,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>72.5</v>
       </c>
       <c r="H2">
         <v>6.3</v>
@@ -1319,16 +1178,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>38.24</v>
+        <v>52.94</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1345,16 +1204,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>63.64</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1380,7 +1239,7 @@
         <v>47.83</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1397,16 +1256,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>84.20999999999999</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1423,16 +1282,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>68.18000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1442,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1474,16 +1333,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920104</v>
+        <v>24330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1497,22 +1356,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920393</v>
+        <v>24330051920394</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1520,22 +1379,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920394</v>
+        <v>24330051920330</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1543,22 +1402,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920330</v>
+        <v>24330051920407</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1566,16 +1425,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920407</v>
+        <v>24330051920260</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1589,39 +1448,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920260</v>
+        <v>24330051920156</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920156</v>
+        <v>24330051920315</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1635,22 +1494,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920315</v>
+        <v>24330051920213</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1658,16 +1517,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920213</v>
+        <v>24330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1687,10 +1546,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1707,13 +1566,13 @@
         <v>24330051920247</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1730,13 +1589,13 @@
         <v>24330051920409</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1756,10 +1615,10 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1779,10 +1638,10 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1799,13 +1658,13 @@
         <v>24330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1825,10 +1684,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1848,10 +1707,10 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1865,91 +1724,91 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920389</v>
+        <v>24330051920113</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920195</v>
+        <v>24330051920308</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920332</v>
+        <v>24330051920400</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920107</v>
+        <v>24330051920388</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1957,22 +1816,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920113</v>
+        <v>24330051920194</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1980,22 +1839,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920143</v>
+        <v>24330051920258</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -2003,160 +1862,160 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920400</v>
+        <v>24330051920392</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920181</v>
+        <v>24330051920403</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920388</v>
+        <v>24330051920155</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920194</v>
+        <v>24330051920144</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920258</v>
+        <v>24330051920355</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920283</v>
+        <v>24330051920182</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920392</v>
+        <v>24330051920406</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2164,22 +2023,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920131</v>
+        <v>24330051920187</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2187,22 +2046,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920155</v>
+        <v>24330051920316</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2210,22 +2069,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920147</v>
+        <v>24330051920201</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2233,22 +2092,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>24330051920144</v>
+        <v>24330051920274</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2256,22 +2115,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920410</v>
+        <v>24330051920267</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2279,22 +2138,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920122</v>
+        <v>24330051920255</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2302,530 +2161,24 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920170</v>
+        <v>24330051920266</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>24330051920355</v>
-      </c>
-      <c r="B39" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>24330051920180</v>
-      </c>
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>24330051920184</v>
-      </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" t="s">
-        <v>142</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>24330051920406</v>
-      </c>
-      <c r="B42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" t="s">
-        <v>143</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>24330051920187</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" t="s">
-        <v>144</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>11</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>24330051920188</v>
-      </c>
-      <c r="B44" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" t="s">
-        <v>145</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>24330051920316</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" t="s">
-        <v>146</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>24330051920206</v>
-      </c>
-      <c r="B46" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>24330051920277</v>
-      </c>
-      <c r="B47" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>24330051920190</v>
-      </c>
-      <c r="B48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>24330051920201</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>24330051920217</v>
-      </c>
-      <c r="B50" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>24330051920228</v>
-      </c>
-      <c r="B51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>24330051920230</v>
-      </c>
-      <c r="B52" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>24330051920246</v>
-      </c>
-      <c r="B53" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" t="s">
-        <v>36</v>
-      </c>
-      <c r="D53" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>24330051920274</v>
-      </c>
-      <c r="B54" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" t="s">
-        <v>154</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>24330051920267</v>
-      </c>
-      <c r="B55" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" t="s">
-        <v>155</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>24330051920255</v>
-      </c>
-      <c r="B56" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" t="s">
-        <v>156</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
-        <v>24330051920257</v>
-      </c>
-      <c r="B57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" t="s">
-        <v>157</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>24330051920391</v>
-      </c>
-      <c r="B58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58" t="s">
-        <v>158</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
-        <v>23330051920189</v>
-      </c>
-      <c r="B59" t="s">
-        <v>36</v>
-      </c>
-      <c r="C59" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60">
-        <v>23330051920211</v>
-      </c>
-      <c r="B60" t="s">
-        <v>43</v>
-      </c>
-      <c r="C60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60">
         <v>1</v>
       </c>
     </row>
